--- a/src/main/resources/excel/사용자등록일괄등록양식.xlsx
+++ b/src/main/resources/excel/사용자등록일괄등록양식.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GD\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66CE42B-0545-42A1-99BA-6D36CEAFD633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E54817-3CBE-48D7-BB17-A6394537B745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5880" yWindow="1875" windowWidth="21450" windowHeight="10470" xr2:uid="{5863148B-EB14-4223-AA0A-3C5721FF3A93}"/>
+    <workbookView xWindow="0" yWindow="1155" windowWidth="27510" windowHeight="12930" xr2:uid="{5863148B-EB14-4223-AA0A-3C5721FF3A93}"/>
   </bookViews>
   <sheets>
     <sheet name="사용자일괄등록양식" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,743 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>GD</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{F285384E-C4F6-4BFA-BE29-36AA05316D2C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사용자</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>세부</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>권한코드</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기입
+관리자</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>권한관리에</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>등록된</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>코드만</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">가능
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ex) S_GRADU04
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{68339965-1074-477E-9206-17AD66396395}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사용자</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>계정</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">상태
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">0 == </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">사용대기
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1 == </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">사용중
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2 == </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">미사용
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">3 == </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>폐지
+해당</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>숫자만</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기입</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>가능</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{AE43FC47-DE32-4F87-A657-AF9A6BCBE94C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">사용자전화번호는
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">"-" </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>하이픈</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">없이
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ex) 01012345678
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{376DEF31-C045-49B2-B544-C02D8C0F9EED}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사용자</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">생년월일은
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">0000-00-00
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>해당</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>양식으로</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">기입
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ex) 2002-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{D37626F3-427E-4C54-91CC-359B9147A232}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>부서코드는
+관리자</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>학과관리에</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>등록된</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>부서코드만</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">가능
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ex)  E1006</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{15E217C1-B4F3-417F-A80A-40EAF6696E90}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>학생인</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>경우에만</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기입</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -83,7 +820,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,6 +835,19 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -122,11 +872,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -442,18 +1195,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{271D1659-717A-482D-835E-A38037B8417C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{271D1659-717A-482D-835E-A38037B8417C}">
   <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -469,13 +1223,13 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -493,7 +1247,7 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -501,5 +1255,6 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>